--- a/results/[3_low_electricity_prices]_#_fix_cost.xlsx
+++ b/results/[3_low_electricity_prices]_#_fix_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3906.399109145206</v>
+        <v>11181.07469447997</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>48353.76274462014</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>9433.134471502228</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2534.277928792104</v>
+        <v>2576.046244458892</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2366.658982337573</v>
+        <v>2999.372804347332</v>
       </c>
       <c r="O2" t="n">
-        <v>1995.412676509708</v>
+        <v>1965.158635784667</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6991.052031681918</v>
+        <v>81680.31588153852</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>197913.7502057619</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16452.51445364119</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8194.52068131253</v>
+        <v>8196.609097095868</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>7540.299372506026</v>
+        <v>12979.0574828046</v>
       </c>
       <c r="O2" t="n">
-        <v>6256.367679449893</v>
+        <v>6253.780164583839</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31236.29455387744</v>
+        <v>130379.7884163835</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>292247.2772138842</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16595.10705160327</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>12131.91920790125</v>
+        <v>12130.38818593496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.527240940757</v>
       </c>
       <c r="N2" t="n">
-        <v>12882.34160925225</v>
+        <v>23864.99915710569</v>
       </c>
       <c r="O2" t="n">
-        <v>9261.533324927314</v>
+        <v>9259.241621239282</v>
       </c>
     </row>
   </sheetData>
@@ -926,13 +926,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>31236.29455387744</v>
+        <v>130379.7884163835</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>292247.2772138842</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -941,13 +941,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16595.10705160327</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>12131.91920790125</v>
+        <v>12130.38818593496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.527240940757</v>
       </c>
       <c r="N2" t="n">
-        <v>14040.19136169543</v>
+        <v>25177.28603607513</v>
       </c>
       <c r="O2" t="n">
-        <v>9261.533324927314</v>
+        <v>9259.241621239282</v>
       </c>
     </row>
   </sheetData>
@@ -1064,13 +1064,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38906.8534480406</v>
+        <v>130379.7884163835</v>
       </c>
       <c r="B2" t="n">
-        <v>193.0947398408091</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>292247.2772138842</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16595.10705160327</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>12131.91920790125</v>
+        <v>12130.38818593496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.527240940757</v>
       </c>
       <c r="N2" t="n">
-        <v>16870.34251754129</v>
+        <v>25177.28603607513</v>
       </c>
       <c r="O2" t="n">
-        <v>10093.83191070589</v>
+        <v>10091.3155236557</v>
       </c>
     </row>
   </sheetData>
@@ -1202,13 +1202,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38906.8534480406</v>
+        <v>130379.7884163835</v>
       </c>
       <c r="B2" t="n">
-        <v>193.0947398408091</v>
+        <v>22664.17018832575</v>
       </c>
       <c r="C2" t="n">
-        <v>292247.2772138842</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16595.10705160327</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>12131.91920790125</v>
+        <v>12130.38818593496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.527240940757</v>
       </c>
       <c r="N2" t="n">
-        <v>16870.34251754129</v>
+        <v>25177.28603607513</v>
       </c>
       <c r="O2" t="n">
-        <v>10093.83191070589</v>
+        <v>10091.3155236557</v>
       </c>
     </row>
   </sheetData>

--- a/results/[3_low_electricity_prices]_#_fix_cost.xlsx
+++ b/results/[3_low_electricity_prices]_#_fix_cost.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2030" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2035" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="2040" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2045" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="2050" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2035" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2040" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2045" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2050" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,13 +512,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5316.139655440329</v>
+        <v>11181.07469447997</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>48354.90449340604</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,13 +527,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>7542.310400722792</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2534.277928792126</v>
+        <v>2576.046244458892</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -551,10 +551,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2317.204104134014</v>
+        <v>2999.372804347332</v>
       </c>
       <c r="O2" t="n">
-        <v>1995.41267650969</v>
+        <v>1965.158635784667</v>
       </c>
     </row>
   </sheetData>
@@ -650,13 +650,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11875.88565627916</v>
+        <v>81680.31588153852</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>189028.2191017097</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>14985.91772494195</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7387.315360922055</v>
+        <v>8196.609097095868</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>7382.188909106125</v>
+        <v>12979.0574828046</v>
       </c>
       <c r="O2" t="n">
-        <v>5756.362569820735</v>
+        <v>6253.780164583839</v>
       </c>
     </row>
   </sheetData>
@@ -788,13 +788,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35028.01430431766</v>
+        <v>130379.7884163835</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>272567.486325675</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -803,13 +803,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16352.18544265527</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>11592.52045454035</v>
+        <v>12130.38818593496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -824,13 +824,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.527240940757</v>
       </c>
       <c r="N2" t="n">
-        <v>13117.60677809189</v>
+        <v>23864.99915710569</v>
       </c>
       <c r="O2" t="n">
-        <v>9654.274888703549</v>
+        <v>9259.241621239282</v>
       </c>
     </row>
   </sheetData>
@@ -926,13 +926,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35028.01430431766</v>
+        <v>130379.7884163835</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>272567.486325675</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -941,13 +941,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16352.18544265527</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>11592.52045454035</v>
+        <v>12130.38818593496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -962,13 +962,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.527240940757</v>
       </c>
       <c r="N2" t="n">
-        <v>13117.60677809189</v>
+        <v>25177.28603607513</v>
       </c>
       <c r="O2" t="n">
-        <v>9654.274888703549</v>
+        <v>9259.241621239282</v>
       </c>
     </row>
   </sheetData>
@@ -1064,13 +1064,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35028.01430431766</v>
+        <v>130379.7884163835</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6159.735574588473</v>
       </c>
       <c r="C2" t="n">
-        <v>272567.486325675</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1079,13 +1079,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16352.18544265527</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>11592.52045454035</v>
+        <v>12130.38818593496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1100,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.527240940757</v>
       </c>
       <c r="N2" t="n">
-        <v>13117.60677809189</v>
+        <v>25177.28603607513</v>
       </c>
       <c r="O2" t="n">
-        <v>9654.274888703549</v>
+        <v>10091.3155236557</v>
       </c>
     </row>
   </sheetData>
@@ -1202,13 +1202,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35028.01430431766</v>
+        <v>130379.7884163835</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>22664.17018832575</v>
       </c>
       <c r="C2" t="n">
-        <v>272567.486325675</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>289724.0114301849</v>
       </c>
       <c r="F2" t="n">
-        <v>16352.18544265527</v>
+        <v>18934.72861703725</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>11592.52045454035</v>
+        <v>12130.38818593496</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -1238,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2652.527240940757</v>
       </c>
       <c r="N2" t="n">
-        <v>13117.60677809189</v>
+        <v>25177.28603607513</v>
       </c>
       <c r="O2" t="n">
-        <v>9654.274888703549</v>
+        <v>10091.3155236557</v>
       </c>
     </row>
   </sheetData>
